--- a/artfynd/A 66483-2021 artfynd.xlsx
+++ b/artfynd/A 66483-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 66483-2021 artfynd.xlsx
+++ b/artfynd/A 66483-2021 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>88367018</v>
       </c>
       <c r="B2" t="n">
-        <v>77588</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79406</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -718,10 +713,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>549490.1230537597</v>
+        <v>549490</v>
       </c>
       <c r="R2" t="n">
-        <v>7126965.156450696</v>
+        <v>7126965</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,19 +746,9 @@
           <t>2020-09-18</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2020-09-18</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
